--- a/astro-site/public/dl/kit-tareas-marisqueria/03-trazabilidad-appcc-marisco.xlsx
+++ b/astro-site/public/dl/kit-tareas-marisqueria/03-trazabilidad-appcc-marisco.xlsx
@@ -1016,7 +1016,7 @@
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
     </row>
-    <row r="22" ht="20" customHeight="1">
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>PCC5</t>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Anisakis: congelacion previa -20°C/7d para consumo crudo/marinado</t>
+          <t>Anisakis: congelación previa −20 °C/24 h (o −35 °C/15 h) si se sirve crudo o marinado</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Obligatorio RD 1420/2006</t>
+          <t>Obligatorio: RD 1021/2022, art. 8.1</t>
         </is>
       </c>
     </row>
